--- a/docs/downloads/20260826_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260826_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1248,6 +1248,58 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>MAIA</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>30141-2</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>UEM Sunrise (Laser Tower S/B)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n">
+        <v>495</v>
+      </c>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="13">
+        <f>W11/$F$11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>Not yet launched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="M3:O3"/>
